--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T12:58:39+05:30</t>
+    <t>2026-05-16T13:10:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
 Identifier.system SHALL follow the naming convention:
 [customer]-[ehr]-[ResourceType]-[resource-subtype]-[eleMent]-[SourceSpecificString]-InternalIdentifier
 Example:
-acme-epic-Patient--identifier-MRN-InternalIdentifier</t>
+acme-cerner-Observation-lab-identifier-AccessionNumber-InternalIdentifier</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T13:10:22+05:30</t>
+    <t>2026-05-16T16:45:26+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -481,7 +481,7 @@
     <t>Identifier.period</t>
   </si>
   <si>
-    <t xml:space="preserve">Period
+    <t xml:space="preserve">Period {http://314e.com/fhir/ig/StructureDefinition/period-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -388,15 +388,14 @@
     <t>Identifier.type</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">CodeableConcept {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}
 </t>
   </si>
   <si>
-    <t>Description of identifier category</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine
-which identifier to use for a specific purpose.</t>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
@@ -503,15 +502,14 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
-    <t>Organization or entity issuing the identifier</t>
-  </si>
-  <si>
-    <t>Organization or entity responsible for issuing
-or managing the identifier.</t>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
   </si>
   <si>
     <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
@@ -838,7 +836,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.47265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="71.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-identifier-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-identifier-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
